--- a/hardware/CPL1.xlsx
+++ b/hardware/CPL1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
   <si>
     <t xml:space="preserve">Designator</t>
   </si>
@@ -40,10 +40,10 @@
     <t xml:space="preserve">C1</t>
   </si>
   <si>
-    <t xml:space="preserve">150.029mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-103.8948mm</t>
+    <t xml:space="preserve">148.228989mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-105.849019mm</t>
   </si>
   <si>
     <t xml:space="preserve">Top</t>
@@ -52,7 +52,10 @@
     <t xml:space="preserve">C2</t>
   </si>
   <si>
-    <t xml:space="preserve">-86.1698mm</t>
+    <t xml:space="preserve">141.1016mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-84.2mm</t>
   </si>
   <si>
     <t xml:space="preserve">J1</t>
@@ -61,7 +64,7 @@
     <t xml:space="preserve">131.979mm</t>
   </si>
   <si>
-    <t xml:space="preserve">-79.4576mm</t>
+    <t xml:space="preserve">-96.7576mm</t>
   </si>
   <si>
     <t xml:space="preserve">J2</t>
@@ -70,64 +73,76 @@
     <t xml:space="preserve">157.379mm</t>
   </si>
   <si>
-    <t xml:space="preserve">J5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.483mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-82.7249mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.973mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-90.616mm</t>
+    <t xml:space="preserve">J3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.443mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-100.606mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.233mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-82.0649mm</t>
   </si>
   <si>
     <t xml:space="preserve">R1</t>
   </si>
   <si>
-    <t xml:space="preserve">141.6165mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-83.1698mm</t>
+    <t xml:space="preserve">141.825mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-81.4mm</t>
   </si>
   <si>
     <t xml:space="preserve">R2</t>
   </si>
   <si>
-    <t xml:space="preserve">145.979mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-100.6698mm</t>
+    <t xml:space="preserve">141.1116mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2mm</t>
   </si>
   <si>
     <t xml:space="preserve">R3</t>
   </si>
   <si>
+    <t xml:space="preserve">148.2364mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-101.8mm</t>
+  </si>
+  <si>
     <t xml:space="preserve">R4</t>
   </si>
   <si>
-    <t xml:space="preserve">141.529mm</t>
+    <t xml:space="preserve">147.525mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-108.6mm</t>
   </si>
   <si>
     <t xml:space="preserve">U1</t>
   </si>
   <si>
-    <t xml:space="preserve">143.6165mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-106.8948mm</t>
+    <t xml:space="preserve">145.5064mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.2075mm</t>
   </si>
   <si>
     <t xml:space="preserve">U2</t>
   </si>
   <si>
-    <t xml:space="preserve">-89.3948mm</t>
+    <t xml:space="preserve">143.9016mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-103.7975mm</t>
   </si>
 </sst>
 </file>
@@ -478,7 +493,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -486,27 +501,27 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
@@ -517,13 +532,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>8</v>
@@ -534,47 +549,47 @@
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>8</v>
@@ -585,87 +600,87 @@
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
